--- a/node-list.xlsx
+++ b/node-list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JMO/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8fe3a1c706bd23a2/Documents/GMU/PHD GMU/RRCHNM/Pepys Network/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{169F1983-2826-264E-AD5C-7B393E8332FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="376" documentId="8_{B9E98637-52DC-4ECC-A499-F4AF383C0930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD556686-8852-470F-BB74-BD35E9DD5DDA}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2160" windowWidth="28040" windowHeight="17440" xr2:uid="{A968A973-8E20-4543-9A9E-06909A6BDDF4}"/>
+    <workbookView xWindow="11442" yWindow="0" windowWidth="11676" windowHeight="12318" xr2:uid="{A968A973-8E20-4543-9A9E-06909A6BDDF4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="210">
   <si>
     <t>id</t>
   </si>
@@ -53,16 +53,634 @@
   </si>
   <si>
     <t>notes</t>
+  </si>
+  <si>
+    <t>home_axe_yard</t>
+  </si>
+  <si>
+    <t>Home Axe Yard</t>
+  </si>
+  <si>
+    <t>exeter_house_chapel</t>
+  </si>
+  <si>
+    <t>Exeter House Chapel</t>
+  </si>
+  <si>
+    <t>Father House</t>
+  </si>
+  <si>
+    <t>Mr Crews House</t>
+  </si>
+  <si>
+    <t>office_exchequer</t>
+  </si>
+  <si>
+    <t>Office Exchequer</t>
+  </si>
+  <si>
+    <t>westminster_hall</t>
+  </si>
+  <si>
+    <t>Westminster Hall</t>
+  </si>
+  <si>
+    <t>Axe Yard, Westminster</t>
+  </si>
+  <si>
+    <t>South of Downing St</t>
+  </si>
+  <si>
+    <t>Covent Garden</t>
+  </si>
+  <si>
+    <t>Palace of Westminster, east side of New Palace Yard</t>
+  </si>
+  <si>
+    <t>Palace of Westminster</t>
+  </si>
+  <si>
+    <t>Turner House</t>
+  </si>
+  <si>
+    <t>turner_house</t>
+  </si>
+  <si>
+    <t>sandwich_lodgings</t>
+  </si>
+  <si>
+    <t>Earl of Sandwich Lodgings</t>
+  </si>
+  <si>
+    <t>Whitehall Palace</t>
+  </si>
+  <si>
+    <t>Salisbury Court</t>
+  </si>
+  <si>
+    <t>John, Jane and Theophila Turner. Madame Morris?</t>
+  </si>
+  <si>
+    <t>Lincoln's Inn Fields?</t>
+  </si>
+  <si>
+    <t>Westminster Palace</t>
+  </si>
+  <si>
+    <t>Managed by Edward Shipley (1659-62), Jemimah Montagu (Carteret after 1665)</t>
+  </si>
+  <si>
+    <t>Wills Ale House</t>
+  </si>
+  <si>
+    <t>Chancery Lane, Temple District</t>
+  </si>
+  <si>
+    <t>whitehall_palace</t>
+  </si>
+  <si>
+    <t>Old Palace Yard</t>
+  </si>
+  <si>
+    <t>swan_inn</t>
+  </si>
+  <si>
+    <t>Swan Inn</t>
+  </si>
+  <si>
+    <t>New Palace Yard</t>
+  </si>
+  <si>
+    <t>John Hunt House</t>
+  </si>
+  <si>
+    <t>John and Elizabeth Hunt</t>
+  </si>
+  <si>
+    <t>the_new_market</t>
+  </si>
+  <si>
+    <t>The New Market</t>
+  </si>
+  <si>
+    <t>fleet_street</t>
+  </si>
+  <si>
+    <t>Fleet Street</t>
+  </si>
+  <si>
+    <t>Mr. Valentine Fage, apothecary</t>
+  </si>
+  <si>
+    <t>harpers_tavern</t>
+  </si>
+  <si>
+    <t>Harpers Tavern</t>
+  </si>
+  <si>
+    <t>King Street</t>
+  </si>
+  <si>
+    <t>Tavern run by Harper family, Mrs. Mary Harper, located outside of King Street gate of Whitehall Palace opposite of Axe Yard</t>
+  </si>
+  <si>
+    <t>thomas_pepys_house</t>
+  </si>
+  <si>
+    <t>Thomas Pepys House</t>
+  </si>
+  <si>
+    <t>Cousin, in 1661 was living in St-Martin-in-the-Fields</t>
+  </si>
+  <si>
+    <t>stradwick_house</t>
+  </si>
+  <si>
+    <t>Stradwick House</t>
+  </si>
+  <si>
+    <t>John Pepys, Tailor, lived south of Fleet Street, St Brides Parish until 1661</t>
+  </si>
+  <si>
+    <t>dr_hoares_house</t>
+  </si>
+  <si>
+    <t>Dr Hoares House</t>
+  </si>
+  <si>
+    <t>Dr. William Hoare</t>
+  </si>
+  <si>
+    <t>Peter Gunning</t>
+  </si>
+  <si>
+    <t>Robert Mossum, Conducted sermons at Cary House in the Strand and St Peter, Pauls Wharf in the 1660s</t>
+  </si>
+  <si>
+    <t>turks_head_coffee_house</t>
+  </si>
+  <si>
+    <t>Turk's Head Coffee House</t>
+  </si>
+  <si>
+    <t>New Palace Yard, Westminster</t>
+  </si>
+  <si>
+    <t>Home of the Rota Club</t>
+  </si>
+  <si>
+    <t>Mentioned in 10 Jan 1659/60</t>
+  </si>
+  <si>
+    <t>John Crew</t>
+  </si>
+  <si>
+    <t>Unknown location and name, 10 jan 1659/60</t>
+  </si>
+  <si>
+    <t>city_of_london</t>
+  </si>
+  <si>
+    <t>Referencing the Royal Exchange?</t>
+  </si>
+  <si>
+    <t>star_tavern</t>
+  </si>
+  <si>
+    <t>Star Tavern</t>
+  </si>
+  <si>
+    <t>Cheapside</t>
+  </si>
+  <si>
+    <t>South side of Cheapside, near Royal Exchange, Francis Ringstead</t>
+  </si>
+  <si>
+    <t>Mother Lams Pub</t>
+  </si>
+  <si>
+    <t>The Half Moon Alehouse</t>
+  </si>
+  <si>
+    <t>Thomas Wade</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>coffee_house_unknown_1</t>
+  </si>
+  <si>
+    <t>tower_menagerie</t>
+  </si>
+  <si>
+    <t>Tower of London Menagerie</t>
+  </si>
+  <si>
+    <t>Tower of London</t>
+  </si>
+  <si>
+    <t>william_joyce_house</t>
+  </si>
+  <si>
+    <t>mr_stevens_house</t>
+  </si>
+  <si>
+    <t>alehouse_unknown_1</t>
+  </si>
+  <si>
+    <t>alehouse_unknown_2</t>
+  </si>
+  <si>
+    <t>wills_alehouse</t>
+  </si>
+  <si>
+    <t>john_crews_house</t>
+  </si>
+  <si>
+    <t>cookshop_unknown_1</t>
+  </si>
+  <si>
+    <t>Cookshop Unknown</t>
+  </si>
+  <si>
+    <t>robert_mossum_church</t>
+  </si>
+  <si>
+    <t>Robert Mossum Church</t>
+  </si>
+  <si>
+    <t>mother_lams_pub</t>
+  </si>
+  <si>
+    <t>the_half_moon_alehouse</t>
+  </si>
+  <si>
+    <t>Thomas and Elizabeth Stradwick, Elizabeth daughter of Richard Pepys</t>
+  </si>
+  <si>
+    <t>john_pepys_house</t>
+  </si>
+  <si>
+    <t>kate_petit_house</t>
+  </si>
+  <si>
+    <t>Walled district between Fleet St and the Thames, Sir Lestrange Calthorpe</t>
+  </si>
+  <si>
+    <t>Lestrange Calthorpe Chamber</t>
+  </si>
+  <si>
+    <t>lestrange_calthorpe_chamber</t>
+  </si>
+  <si>
+    <t>George Vines, Deputy Chamberlain of the Receipt of the Exchequer</t>
+  </si>
+  <si>
+    <t>george_vines_house</t>
+  </si>
+  <si>
+    <t>George Vines House</t>
+  </si>
+  <si>
+    <t>john_hunt_house</t>
+  </si>
+  <si>
+    <t>valentine_fage_house</t>
+  </si>
+  <si>
+    <t>Valentine Fage House</t>
+  </si>
+  <si>
+    <t>thomas_wade_house</t>
+  </si>
+  <si>
+    <t>Thomas Wade House</t>
+  </si>
+  <si>
+    <t>market_unknown_1</t>
+  </si>
+  <si>
+    <t>alehouse_unknown_3</t>
+  </si>
+  <si>
+    <t>salisbury_court</t>
+  </si>
+  <si>
+    <t>Alehouse Unknown</t>
+  </si>
+  <si>
+    <t>Market Unknown</t>
+  </si>
+  <si>
+    <t>Kate Petit House</t>
+  </si>
+  <si>
+    <t>Mr Stevens House</t>
+  </si>
+  <si>
+    <t>William Joyce House</t>
+  </si>
+  <si>
+    <t>Coffeehouse Unknown</t>
+  </si>
+  <si>
+    <t>Blackfriars</t>
+  </si>
+  <si>
+    <t>Between Fleet Street and Dorset Stairs on the Thames</t>
+  </si>
+  <si>
+    <t>parish_clerks_hall</t>
+  </si>
+  <si>
+    <t>green_dragon_pub</t>
+  </si>
+  <si>
+    <t>Lambeth Hill</t>
+  </si>
+  <si>
+    <t>Lambeth Hill, Upper Thames Street</t>
+  </si>
+  <si>
+    <t>golden_lion_pub</t>
+  </si>
+  <si>
+    <t>Charing Cross</t>
+  </si>
+  <si>
+    <t>twickenham</t>
+  </si>
+  <si>
+    <t>william_fuller_lodging</t>
+  </si>
+  <si>
+    <t>brentford</t>
+  </si>
+  <si>
+    <t>wilkinsons_cookshop</t>
+  </si>
+  <si>
+    <t>King Street, Westminster</t>
+  </si>
+  <si>
+    <t>Between Sea Alley and Axe Yard, kept by William Wilkinson</t>
+  </si>
+  <si>
+    <t>george_downings_lodgings</t>
+  </si>
+  <si>
+    <t>George Downings Lodgings</t>
+  </si>
+  <si>
+    <t>Parish Clerks Hall</t>
+  </si>
+  <si>
+    <t>Green Dragon Pub</t>
+  </si>
+  <si>
+    <t>Golden Lion Pub</t>
+  </si>
+  <si>
+    <t>harp_and_ball_tavern</t>
+  </si>
+  <si>
+    <t>french_ordinary</t>
+  </si>
+  <si>
+    <t>james_marsh_lodgings</t>
+  </si>
+  <si>
+    <t>the_swan_pub</t>
+  </si>
+  <si>
+    <t>Old Fish Street</t>
+  </si>
+  <si>
+    <t>South of St Paul's Cathedral</t>
+  </si>
+  <si>
+    <t>coffee_house_unknown_2</t>
+  </si>
+  <si>
+    <t>mr_sheply_lodgings</t>
+  </si>
+  <si>
+    <t>mr_vernon_lodging</t>
+  </si>
+  <si>
+    <t>Possibly John Vernon Quarter-master general</t>
+  </si>
+  <si>
+    <t>mitre_tavern</t>
+  </si>
+  <si>
+    <t>Hugh Steadman</t>
+  </si>
+  <si>
+    <t>clerks_room_whitehall</t>
+  </si>
+  <si>
+    <t>st_brides_church</t>
+  </si>
+  <si>
+    <t>John Herring vicar of St Brides</t>
+  </si>
+  <si>
+    <t>axe_brewhouse</t>
+  </si>
+  <si>
+    <t>Axe Yard off King Street, now Fludyer Street</t>
+  </si>
+  <si>
+    <t>stone_gallery_whitehall</t>
+  </si>
+  <si>
+    <t>cockpit_whitehall</t>
+  </si>
+  <si>
+    <t>james_pearse_house</t>
+  </si>
+  <si>
+    <t>thomas_pepys_shop</t>
+  </si>
+  <si>
+    <t>St. Paul's Churchyard</t>
+  </si>
+  <si>
+    <t>william_wight_house</t>
+  </si>
+  <si>
+    <t>Samuel Pepys' uncle</t>
+  </si>
+  <si>
+    <t>st_pauls_churchyard</t>
+  </si>
+  <si>
+    <t>william_jessop_lodging</t>
+  </si>
+  <si>
+    <t>crown_pub</t>
+  </si>
+  <si>
+    <t>george_montagu_house</t>
+  </si>
+  <si>
+    <t>royal_exchange</t>
+  </si>
+  <si>
+    <t>heaven_alehouse</t>
+  </si>
+  <si>
+    <t>Adjacent to Westminster Hall</t>
+  </si>
+  <si>
+    <t>st_clements_church</t>
+  </si>
+  <si>
+    <t>anne_wright_house</t>
+  </si>
+  <si>
+    <t>peter_gunning_church</t>
+  </si>
+  <si>
+    <t>mr_torriano_house</t>
+  </si>
+  <si>
+    <t>richard_matthews_house</t>
+  </si>
+  <si>
+    <t>star_chamber_westminster</t>
+  </si>
+  <si>
+    <t>east side of new palace yard</t>
+  </si>
+  <si>
+    <t>Twickenham</t>
+  </si>
+  <si>
+    <t>William Fuller Lodging</t>
+  </si>
+  <si>
+    <t>Brentford</t>
+  </si>
+  <si>
+    <t>Harp And Ball Tavern</t>
+  </si>
+  <si>
+    <t>James Marsh Lodgings</t>
+  </si>
+  <si>
+    <t>The Swan Pub</t>
+  </si>
+  <si>
+    <t>Coffee House Unknown 2</t>
+  </si>
+  <si>
+    <t>Mr Sheply Lodgings</t>
+  </si>
+  <si>
+    <t>Mr Vernon Lodging</t>
+  </si>
+  <si>
+    <t>Clerks Room Whitehall</t>
+  </si>
+  <si>
+    <t>St Brides Church</t>
+  </si>
+  <si>
+    <t>Stone Gallery Whitehall</t>
+  </si>
+  <si>
+    <t>James Pearse House</t>
+  </si>
+  <si>
+    <t>Thomas Pepys Shop</t>
+  </si>
+  <si>
+    <t>William Wight House</t>
+  </si>
+  <si>
+    <t>St Pauls Churchyard</t>
+  </si>
+  <si>
+    <t>William Jessop Lodging</t>
+  </si>
+  <si>
+    <t>George Montagu House</t>
+  </si>
+  <si>
+    <t>Anne Wright House</t>
+  </si>
+  <si>
+    <t>Peter Gunning Church</t>
+  </si>
+  <si>
+    <t>Mr Torriano House</t>
+  </si>
+  <si>
+    <t>Richard Matthews House</t>
+  </si>
+  <si>
+    <t>Star Chamber Westminster</t>
+  </si>
+  <si>
+    <t>Crown Pub</t>
+  </si>
+  <si>
+    <t>Axe Brewhouse</t>
+  </si>
+  <si>
+    <t>Heaven Alehouse</t>
+  </si>
+  <si>
+    <t>Royal Exchange</t>
+  </si>
+  <si>
+    <t>Mitre Tavern</t>
+  </si>
+  <si>
+    <t>French Ordinary</t>
+  </si>
+  <si>
+    <t>Wilkinson's Cookshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brentford </t>
+  </si>
+  <si>
+    <t>Sister of Jemima Montagu, wife of Sir Henry Wright</t>
+  </si>
+  <si>
+    <t>St Clement Danes Church</t>
+  </si>
+  <si>
+    <t>Westminster, London</t>
+  </si>
+  <si>
+    <t>Cockpit-in-Court Whitehall</t>
+  </si>
+  <si>
+    <t>Ground floor of Whitehall, parallel to the Thames, below the Matted Gallery</t>
+  </si>
+  <si>
+    <t>Old Palace Yard, Westminster</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -88,8 +706,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -107,10 +731,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -148,7 +776,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -254,7 +882,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -396,7 +1024,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -404,10 +1032,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBCA395E-755B-9741-9FA5-95184354E323}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F76"/>
+  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -425,6 +1059,978 @@
       </c>
       <c r="F1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2">
+        <v>51.502912000000002</v>
+      </c>
+      <c r="E2">
+        <v>-0.12725900000000001</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>51.511377000000003</v>
+      </c>
+      <c r="E3">
+        <v>-0.12012399999999999</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4">
+        <v>51.513500000000001</v>
+      </c>
+      <c r="E4">
+        <v>-0.10630000000000001</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5">
+        <v>51.513500000000001</v>
+      </c>
+      <c r="E5">
+        <v>-0.10630000000000001</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7">
+        <v>51.512622</v>
+      </c>
+      <c r="E7">
+        <v>-0.11026</v>
+      </c>
+      <c r="F7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9">
+        <v>51.500304999999997</v>
+      </c>
+      <c r="E9">
+        <v>-0.124485</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>51.500047000000002</v>
+      </c>
+      <c r="E10">
+        <v>-0.12521599999999999</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>51.504443999999999</v>
+      </c>
+      <c r="E14">
+        <v>-0.125556</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="1">
+        <v>51.503582000000002</v>
+      </c>
+      <c r="E19">
+        <v>-0.12584899999999999</v>
+      </c>
+      <c r="F19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A29" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30">
+        <v>51.509692999999999</v>
+      </c>
+      <c r="E30">
+        <v>-0.12391199999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A31" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A32" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A33" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A34" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A36" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A38" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A39" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A40" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" t="s">
+        <v>110</v>
+      </c>
+      <c r="C40" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A41" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
+        <v>116</v>
+      </c>
+      <c r="D41">
+        <v>51.513824</v>
+      </c>
+      <c r="E41">
+        <v>-0.106214</v>
+      </c>
+      <c r="F41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A42" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A43" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" t="s">
+        <v>133</v>
+      </c>
+      <c r="C43" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A44" t="s">
+        <v>122</v>
+      </c>
+      <c r="B44" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A45" t="s">
+        <v>124</v>
+      </c>
+      <c r="B45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A46" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A47" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" t="s">
+        <v>175</v>
+      </c>
+      <c r="C47" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A48" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" t="s">
+        <v>202</v>
+      </c>
+      <c r="C48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A49" t="s">
+        <v>135</v>
+      </c>
+      <c r="B49" t="s">
+        <v>176</v>
+      </c>
+      <c r="C49" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A50" t="s">
+        <v>136</v>
+      </c>
+      <c r="B50" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A51" t="s">
+        <v>137</v>
+      </c>
+      <c r="B51" t="s">
+        <v>177</v>
+      </c>
+      <c r="C51" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A52" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" t="s">
+        <v>178</v>
+      </c>
+      <c r="C52" t="s">
+        <v>139</v>
+      </c>
+      <c r="F52" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A53" t="s">
+        <v>141</v>
+      </c>
+      <c r="B53" t="s">
+        <v>179</v>
+      </c>
+      <c r="C53" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A54" t="s">
+        <v>142</v>
+      </c>
+      <c r="B54" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A55" t="s">
+        <v>143</v>
+      </c>
+      <c r="B55" t="s">
+        <v>181</v>
+      </c>
+      <c r="C55" t="s">
+        <v>76</v>
+      </c>
+      <c r="F55" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A56" t="s">
+        <v>145</v>
+      </c>
+      <c r="B56" t="s">
+        <v>200</v>
+      </c>
+      <c r="C56" t="s">
+        <v>43</v>
+      </c>
+      <c r="D56">
+        <v>51.513933999999999</v>
+      </c>
+      <c r="E56">
+        <v>-0.109665</v>
+      </c>
+      <c r="F56" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A57" t="s">
+        <v>147</v>
+      </c>
+      <c r="B57" t="s">
+        <v>182</v>
+      </c>
+      <c r="C57" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A58" t="s">
+        <v>148</v>
+      </c>
+      <c r="B58" t="s">
+        <v>183</v>
+      </c>
+      <c r="C58" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58">
+        <v>51.513724000000003</v>
+      </c>
+      <c r="E58">
+        <v>-0.105616</v>
+      </c>
+      <c r="F58" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A59" t="s">
+        <v>150</v>
+      </c>
+      <c r="B59" t="s">
+        <v>197</v>
+      </c>
+      <c r="C59" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59">
+        <v>51.502876000000001</v>
+      </c>
+      <c r="E59">
+        <v>-0.12779399999999999</v>
+      </c>
+      <c r="F59" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A60" t="s">
+        <v>152</v>
+      </c>
+      <c r="B60" t="s">
+        <v>184</v>
+      </c>
+      <c r="C60" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60">
+        <v>51.503867999999997</v>
+      </c>
+      <c r="E60">
+        <v>-0.124712</v>
+      </c>
+      <c r="F60" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A61" t="s">
+        <v>153</v>
+      </c>
+      <c r="B61" t="s">
+        <v>207</v>
+      </c>
+      <c r="C61" t="s">
+        <v>25</v>
+      </c>
+      <c r="D61">
+        <v>51.503906999999998</v>
+      </c>
+      <c r="E61">
+        <v>-0.12729699999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A62" t="s">
+        <v>154</v>
+      </c>
+      <c r="B62" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A63" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" t="s">
+        <v>156</v>
+      </c>
+      <c r="D63">
+        <v>51.514344000000001</v>
+      </c>
+      <c r="E63">
+        <v>-9.7778000000000004E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A64" t="s">
+        <v>157</v>
+      </c>
+      <c r="B64" t="s">
+        <v>187</v>
+      </c>
+      <c r="F64" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A65" t="s">
+        <v>159</v>
+      </c>
+      <c r="B65" t="s">
+        <v>188</v>
+      </c>
+      <c r="C65" t="s">
+        <v>156</v>
+      </c>
+      <c r="D65">
+        <v>51.514344000000001</v>
+      </c>
+      <c r="E65">
+        <v>-9.7778000000000004E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A66" t="s">
+        <v>160</v>
+      </c>
+      <c r="B66" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A67" t="s">
+        <v>161</v>
+      </c>
+      <c r="B67" t="s">
+        <v>196</v>
+      </c>
+      <c r="C67" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A68" t="s">
+        <v>162</v>
+      </c>
+      <c r="B68" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A69" t="s">
+        <v>163</v>
+      </c>
+      <c r="B69" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A70" t="s">
+        <v>164</v>
+      </c>
+      <c r="B70" t="s">
+        <v>198</v>
+      </c>
+      <c r="C70" t="s">
+        <v>209</v>
+      </c>
+      <c r="F70" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A71" t="s">
+        <v>166</v>
+      </c>
+      <c r="B71" t="s">
+        <v>205</v>
+      </c>
+      <c r="C71" t="s">
+        <v>206</v>
+      </c>
+      <c r="D71">
+        <v>51.513106999999998</v>
+      </c>
+      <c r="E71">
+        <v>-0.113898</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A72" t="s">
+        <v>167</v>
+      </c>
+      <c r="B72" t="s">
+        <v>191</v>
+      </c>
+      <c r="F72" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A73" t="s">
+        <v>168</v>
+      </c>
+      <c r="B73" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A74" t="s">
+        <v>169</v>
+      </c>
+      <c r="B74" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A75" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A76" t="s">
+        <v>171</v>
+      </c>
+      <c r="B76" t="s">
+        <v>195</v>
+      </c>
+      <c r="C76" t="s">
+        <v>29</v>
+      </c>
+      <c r="D76">
+        <v>51.500500000000002</v>
+      </c>
+      <c r="E76">
+        <v>-0.12479999999999999</v>
+      </c>
+      <c r="F76" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/node-list.xlsx
+++ b/node-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="nodes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2132,8 +2132,952 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>downings_counsellor_chamber</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Mr Downings Counsellor Chamber</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mr Downing's counsel, visited 1 Feb 1659/60; possibly Mr Stephens, the counsellor at the Temple (cf. 4 and 10 Feb) - unconfirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>lincolns_inn</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Lincoln's Inn</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Holborn</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Inn of Court; "Lincoln's Inn Court" 4 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>chequers_inn</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>The Chequers</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Charing Cross</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>"the Exchequer at Charing Cross" 2 Feb, "the Chequers" 5 and 11 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>calthrop_grocer_house</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Mr Calthrop Grocer House</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>London Bridge</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mr Calthrop, a grocer - distinct from Sir Lestrange Calthorpe of the Temple</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>bridge_tavern</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Bridge Tavern</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>London Bridge</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>the_strand</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>The Strand</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Landing place, "over against Somerset House", 2 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>mrs_johnson_house</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Mrs Johnson House</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>The Strand</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mrs Johnson, the Earl of Sandwich's sempstress</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>st_jamess_park</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>St James's Park</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>guard_chamber_whitehall</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Guard Chamber Whitehall</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Whitehall Palace</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>house_of_commons</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>House of Commons</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Westminster Palace</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>"the manner of the Houses sitting" 3 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>priors_rhenish_wine_house</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Priors Rhenish Wine House</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>"Priors, the Rhenish wine-house" 3 Feb; "a Rhenish wine house" 8 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>palace_yard_westminster</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Palace Yard Westminster</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Westminster Palace</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>The entry does not say whether New or Old Palace Yard</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>charing_cross</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Charing Cross</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>swan_house</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Mr Swan House</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mr Swan, of the Exchequer</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>stephens_chamber_temple</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Mr Stephens Chamber</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>The Temple</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>"the Counsellor at the Temple, Mr. Stephens" 4 Feb; "Mr. Stevens our lawyer" 10 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>grays_inn</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Gray's Inn</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Holborn</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Inn of Court</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_4</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Alehouse Unknown</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Holborn</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>"we met with an acquaintance of his in the walks, and went and drank" 4 Feb 1659/60 - drinking house near Gray's Inn, unnamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>lord_widdrington_house</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Lord Widdrington House</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mr Swan's master</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Scott House</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Madam Scott and her husband, cf. 1 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>bull_head_tavern</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Bull Head Tavern</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>the_temple</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>The Temple</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Temple district</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Area-level node for "the Temple" where no chamber is named</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>st_pauls_school</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>St Paul's School</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>St. Paul's Churchyard</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Pepys's own school; his brother John was a pupil</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>captain_stone_lodgings</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Captain Stone Lodgings</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Captain Stone, concerned in Mr Downing's business</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>temple_gardens</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Temple Gardens</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>The Temple</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>wheeler_house</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sir N Wheeler House</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Sir Nicholas Wheeler</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>phelps_house</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Mr Phelps House</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>upper_bench_court</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Upper Bench</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Westminster Hall</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Court of Upper Bench, sitting in Westminster Hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>sugar_loaf_tavern</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sugar Loaf Tavern</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Temple Bar</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>"a drinking-house near Temple Bar" 9 Feb, named "the Sugar Loaf by Temple Bar, where Swan and I were last night" 10 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>court_of_wards</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Court of Wards</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>exchequer_court</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Court of Exchequer</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Westminster Palace</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>"the Exchequer, where the Barons were hearing of causes" - the court, distinct from office_exchequer, Mr Downing's office</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>commons_lobby</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>House of Commons Lobby</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Westminster Palace</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cookshop_unknown_2</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Cookshop Unknown</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Temple Bar</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>"within Temple Bar, we found a pullet ready roasted" 11 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>the_rolls</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>The Rolls</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Chancery Lane</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Rolls Office and Chapel</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>chetwind_office</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Mr Chetwind Office</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Chancery Lane</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>guildhall</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Guildhall</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr"/>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>three_tuns_tavern</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Three Tuns Tavern</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>"the 3 Tun tavern", near Guildhall</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_5</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Alehouse Unknown</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Unnamed alehouse near Guildhall, 11 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>merchant_house_unknown_1</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Merchant House Unknown</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>"a merchant's house hard by" Guildhall, 11 Feb 1659/60; Sir Nicholas Crisp was there</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>moorfields</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Moorfields</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>playfords_shop</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Playford Shop</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>John Playford, music seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cumberland_lodgings</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Mr Cumberland Lodgings</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Richard Cumberland, "newly come out of the country from his living" 5 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>hering_house</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Mr Hering House</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Hering the merchant, concerned in my Lord's Worcester money</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>new_exchange</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>The New Exchange</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>The Strand</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Shopping arcade on the south side of the Strand; distinct from the Royal Exchange in the City</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F78"/>
+  <autoFilter ref="A1:F121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/node-list.xlsx
+++ b/node-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="nodes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1072,13 +1072,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Referencing the Royal Exchange?</t>
+          <t>City of London</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Referencing the Royal Exchange?</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1995,12 +1999,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>anne_wright_house</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Anne Wright House</t>
+          <t>Wright House</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -2008,7 +2012,7 @@
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sister of Jemima Montagu, wife of Sir Henry Wright</t>
+          <t>Henry and Anne Wright, Anne sister of Jemima Montagu, wife of Sir Henry Wright</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2095,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>the_sun_pub</t>
+          <t>the_sun_tavern</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2196,19 +2200,19 @@
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>"the Exchequer at Charing Cross" 2 Feb, "the Chequers" 5 and 11 Feb 1659/60</t>
+          <t>An inn and ordinary. "the Exchequer at Charing Cross" 2 Feb, "the Chequers" 5 and 11 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>calthrop_grocer_house</t>
+          <t>edward_calthrop_grocer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mr Calthrop Grocer House</t>
+          <t>Edward Calthrop Grocer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2288,14 +2292,14 @@
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mrs Johnson, the Earl of Sandwich's sempstress</t>
+          <t>Mrs Johnson, the Earl of Sandwich's seamstress</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>st_jamess_park</t>
+          <t>st_james_park</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2376,7 +2380,7 @@
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>"Priors, the Rhenish wine-house" 3 Feb; "a Rhenish wine house" 8 Feb 1659/60</t>
+          <t>Cannon Row, Westminster, at the end of passage leading from King Street. "Priors, the Rhenish wine-house" 3 Feb; "a Rhenish wine house" 8 Feb 1659/60</t>
         </is>
       </c>
     </row>
@@ -2427,12 +2431,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>swan_house</t>
+          <t>william_swan_house</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mr Swan House</t>
+          <t>William Swan House</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2440,7 +2444,7 @@
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mr Swan, of the Exchequer</t>
+          <t>William Swan, of the Exchequer</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2523,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>lord_widdrington_house</t>
+          <t>thomas_widdrington_house</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lord Widdrington House</t>
+          <t>Lord Thomas Widdrington House</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2623,12 +2627,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>captain_stone_lodgings</t>
+          <t>john_stone_office</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Captain Stone Lodgings</t>
+          <t>Captain John Stone Office</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2663,12 +2667,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>wheeler_house</t>
+          <t>william_wheeler_house</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sir N Wheeler House</t>
+          <t>Sir William Wheeler House</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2676,19 +2680,19 @@
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sir Nicholas Wheeler</t>
+          <t>Sir William Wheeler</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>phelps_house</t>
+          <t>john_phelps_house</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mr Phelps House</t>
+          <t>John Phelps House</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2736,11 +2740,15 @@
           <t>Temple Bar</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr"/>
-      <c r="E106" s="2" t="inlineStr"/>
+      <c r="D106" s="2" t="n">
+        <v>51.513455</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>-0.111742</v>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>"a drinking-house near Temple Bar" 9 Feb, named "the Sugar Loaf by Temple Bar, where Swan and I were last night" 10 Feb 1659/60</t>
+          <t>Fleet Street, "a drinking-house near Temple Bar" 9 Feb, named "the Sugar Loaf by Temple Bar, where Swan and I were last night" 10 Feb 1659/60</t>
         </is>
       </c>
     </row>
@@ -2835,12 +2843,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>the_rolls</t>
+          <t>rolls_office_chancery</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The Rolls</t>
+          <t>The Rolls Office</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2859,12 +2867,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>chetwind_office</t>
+          <t>james_chetwind_office</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Mr Chetwind Office</t>
+          <t>James Chetwind Office</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2909,7 +2917,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>City of London</t>
+          <t>Guildhall Yard</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
@@ -2984,19 +2992,27 @@
           <t>City of London</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr"/>
-      <c r="E117" s="2" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="D117" s="2" t="n">
+        <v>51.519038</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>-0.086882</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Near the Moorgate, divided into three areas Moorfields proper, Middle and Upper, near Bethlem Hospital Moorfields</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>playfords_shop</t>
+          <t>john_playford_shop</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Playford Shop</t>
+          <t>John Playford Shop</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -3011,12 +3027,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>cumberland_lodgings</t>
+          <t>richard_cumberland_lodgings</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mr Cumberland Lodgings</t>
+          <t>Richard Cumberland Lodgings</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -3031,12 +3047,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>hering_house</t>
+          <t>michael_hering_house</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Mr Hering House</t>
+          <t>Michael Hering House</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3048,7 +3064,7 @@
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hering the merchant, concerned in my Lord's Worcester money</t>
+          <t>Possibly located on Coleman Street, Hering the merchant, concerned in my Lord's Worcester money</t>
         </is>
       </c>
     </row>
@@ -3076,8 +3092,32 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>new_palace_yard_westminster</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>New Palace Yard</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Westminster Palace</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>"then to the Hall, where in the Palace I saw Monk's soldiers abuse Billing and all the Quakers" 7 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F121"/>
+  <autoFilter ref="A1:F122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/node-list.xlsx
+++ b/node-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="nodes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F122"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Peter Gunning</t>
+          <t>Peter Gunning preached here; "to Mr. Gunning" 29 Jan and 5 Feb 1659/60 refer to this chapel</t>
         </is>
       </c>
     </row>
@@ -2019,12 +2019,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>peter_gunning_church</t>
+          <t>mr_torriano_house</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Peter Gunning Church</t>
+          <t>Mr Torriano House</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -2035,12 +2035,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>mr_torriano_house</t>
+          <t>richard_matthews_house</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mr Torriano House</t>
+          <t>Richard Matthews House</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -2051,212 +2051,224 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>richard_matthews_house</t>
+          <t>star_chamber_westminster</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Richard Matthews House</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+          <t>Star Chamber Westminster</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Westminster Palace</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>51.5005</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>-0.1248</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>east side of new palace yard</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>star_chamber_westminster</t>
+          <t>the_sun_tavern</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Star Chamber Westminster</t>
+          <t>The Sun Tavern</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Westminster Palace</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>51.5005</v>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>-0.1248</v>
-      </c>
+          <t>Chancery Lane</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>east side of new palace yard</t>
+          <t>"the Sun in Chancery Lane", 20 Jan 1659/60</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>the_sun_tavern</t>
+          <t>richard_sherwin_office</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Sun Tavern</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Chancery Lane</t>
-        </is>
-      </c>
+          <t>Richard Sherwin Office</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>"the Sun in Chancery Lane", 20 Jan 1659/60</t>
+          <t>Richard Sherwin; Pepys sent there by Mr Downing, 27 Jan 1659/60</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>richard_sherwin_office</t>
+          <t>lincolns_inn</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Richard Sherwin Office</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>Lincoln's Inn</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Holborn</t>
+        </is>
+      </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Richard Sherwin; Pepys sent there by Mr Downing, 27 Jan 1659/60</t>
+          <t>Inn of Court; "Lincoln's Inn Court" 4 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>downings_counsellor_chamber</t>
+          <t>chequers_inn</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mr Downings Counsellor Chamber</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>The Chequers</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Charing Cross</t>
+        </is>
+      </c>
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mr Downing's counsel, visited 1 Feb 1659/60; possibly Mr Stephens, the counsellor at the Temple (cf. 4 and 10 Feb) - unconfirmed</t>
+          <t>An inn and ordinary. "the Chequers" 5 and 11 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>lincolns_inn</t>
+          <t>edward_calthrop_grocer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lincoln's Inn</t>
+          <t>Edward Calthrop Grocer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Holborn</t>
+          <t>London Bridge</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Inn of Court; "Lincoln's Inn Court" 4 Feb 1659/60</t>
+          <t>Mr Calthrop, a grocer - distinct from Sir Lestrange Calthorpe of the Temple</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>chequers_inn</t>
+          <t>bridge_tavern</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The Chequers</t>
+          <t>Bridge Tavern</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charing Cross</t>
+          <t>London Bridge</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>An inn and ordinary. "the Exchequer at Charing Cross" 2 Feb, "the Chequers" 5 and 11 Feb 1659/60</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>edward_calthrop_grocer</t>
+          <t>the_strand</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Edward Calthrop Grocer</t>
+          <t>The Strand</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>London Bridge</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mr Calthrop, a grocer - distinct from Sir Lestrange Calthorpe of the Temple</t>
+          <t>Landing place, "over against Somerset House", 2 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>bridge_tavern</t>
+          <t>mrs_johnson_house</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bridge Tavern</t>
+          <t>Mrs Johnson House</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>London Bridge</t>
+          <t>The Strand</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mrs Johnson, the Earl of Sandwich's seamstress</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>the_strand</t>
+          <t>st_james_park</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Strand</t>
+          <t>St James's Park</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2266,85 +2278,85 @@
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Landing place, "over against Somerset House", 2 Feb 1659/60</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mrs_johnson_house</t>
+          <t>guard_chamber_whitehall</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mrs Johnson House</t>
+          <t>Guard Chamber Whitehall</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>The Strand</t>
+          <t>Whitehall Palace</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Mrs Johnson, the Earl of Sandwich's seamstress</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>st_james_park</t>
+          <t>house_of_commons</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>St James's Park</t>
+          <t>House of Commons</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Westminster</t>
+          <t>Westminster Palace</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>"the manner of the Houses sitting" 3 Feb 1659/60</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>guard_chamber_whitehall</t>
+          <t>priors_rhenish_wine_house</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Guard Chamber Whitehall</t>
+          <t>Priors Rhenish Wine House</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Whitehall Palace</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Cannon Row, Westminster, at the end of passage leading from King Street. "Priors, the Rhenish wine-house" 3 Feb; "a Rhenish wine house" 8 Feb 1659/60</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>house_of_commons</t>
+          <t>palace_yard_westminster</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>House of Commons</t>
+          <t>Palace Yard Westminster</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2356,19 +2368,19 @@
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>"the manner of the Houses sitting" 3 Feb 1659/60</t>
+          <t>The entry does not say whether New or Old Palace Yard</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>priors_rhenish_wine_house</t>
+          <t>charing_cross</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Priors Rhenish Wine House</t>
+          <t>Charing Cross</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2378,261 +2390,253 @@
       </c>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Cannon Row, Westminster, at the end of passage leading from King Street. "Priors, the Rhenish wine-house" 3 Feb; "a Rhenish wine house" 8 Feb 1659/60</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>palace_yard_westminster</t>
+          <t>william_swan_house</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Palace Yard Westminster</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Westminster Palace</t>
-        </is>
-      </c>
+          <t>William Swan House</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>The entry does not say whether New or Old Palace Yard</t>
+          <t>William Swan, of the Exchequer</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>charing_cross</t>
+          <t>stephens_chamber_temple</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Charing Cross</t>
+          <t>Mr Stephens Chamber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Westminster</t>
+          <t>The Temple</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>"Mr. Downing's Counsellor" 1 Feb; "the Counsellor at the Temple, Mr. Stephens" 4 Feb; "Mr. Stevens our lawyer" 10 Feb 1659/60 - one person, acting in the Downing/Squib case throughout</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>william_swan_house</t>
+          <t>grays_inn</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>William Swan House</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>Gray's Inn</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Holborn</t>
+        </is>
+      </c>
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>William Swan, of the Exchequer</t>
+          <t>Inn of Court</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>stephens_chamber_temple</t>
+          <t>alehouse_unknown_4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mr Stephens Chamber</t>
+          <t>Alehouse Unknown</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>The Temple</t>
+          <t>Holborn</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>"the Counsellor at the Temple, Mr. Stephens" 4 Feb; "Mr. Stevens our lawyer" 10 Feb 1659/60</t>
+          <t>"we met with an acquaintance of his in the walks, and went and drank" 4 Feb 1659/60 - drinking house near Gray's Inn, unnamed</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>grays_inn</t>
+          <t>thomas_widdrington_house</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Gray's Inn</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Holborn</t>
-        </is>
-      </c>
+          <t>Lord Thomas Widdrington House</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Inn of Court</t>
+          <t>Mr Swan's master</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>alehouse_unknown_4</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Alehouse Unknown</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Holborn</t>
-        </is>
-      </c>
+          <t>Scott House</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>"we met with an acquaintance of his in the walks, and went and drank" 4 Feb 1659/60 - drinking house near Gray's Inn, unnamed</t>
+          <t>Madam Scott and her husband. Mrs Jem (Jemima Montagu) lodges here through February 1659/60, with Mrs Ann; 4 Feb places both at Scott's explicitly</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>thomas_widdrington_house</t>
+          <t>bull_head_tavern</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lord Thomas Widdrington House</t>
+          <t>Bull Head Tavern</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Mr Swan's master</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>scott_house</t>
+          <t>the_temple</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Scott House</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>The Temple</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Temple district</t>
+        </is>
+      </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Madam Scott and her husband, cf. 1 Feb 1659/60</t>
+          <t>Area-level node for "the Temple" where no chamber is named</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>bull_head_tavern</t>
+          <t>st_pauls_school</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bull Head Tavern</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>St Paul's School</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>St. Paul's Churchyard</t>
+        </is>
+      </c>
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Pepys's own school; his brother John was a pupil</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>the_temple</t>
+          <t>john_stone_office</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Temple</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Temple district</t>
-        </is>
-      </c>
+          <t>Captain John Stone Office</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Area-level node for "the Temple" where no chamber is named</t>
+          <t>Captain Stone, concerned in Mr Downing's business</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>st_pauls_school</t>
+          <t>temple_gardens</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>St Paul's School</t>
+          <t>Temple Gardens</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>St. Paul's Churchyard</t>
+          <t>The Temple</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Pepys's own school; his brother John was a pupil</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>john_stone_office</t>
+          <t>william_wheeler_house</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Captain John Stone Office</t>
+          <t>Sir William Wheeler House</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2640,26 +2644,22 @@
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Captain Stone, concerned in Mr Downing's business</t>
+          <t>Sir William Wheeler</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>temple_gardens</t>
+          <t>john_phelps_house</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Temple Gardens</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>The Temple</t>
-        </is>
-      </c>
+          <t>John Phelps House</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
@@ -2667,105 +2667,113 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>william_wheeler_house</t>
+          <t>upper_bench_court</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sir William Wheeler House</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>Upper Bench</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Westminster Hall</t>
+        </is>
+      </c>
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sir William Wheeler</t>
+          <t>Court of Upper Bench, sitting in Westminster Hall</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>john_phelps_house</t>
+          <t>sugar_loaf_tavern</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>John Phelps House</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" s="2" t="inlineStr"/>
-      <c r="E104" s="2" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+          <t>Sugar Loaf Tavern</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Temple Bar</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>51.513455</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>-0.111742</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Fleet Street, "a drinking-house near Temple Bar" 9 Feb, named "the Sugar Loaf by Temple Bar, where Swan and I were last night" 10 Feb 1659/60</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>upper_bench_court</t>
+          <t>court_of_wards</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Upper Bench</t>
+          <t>Court of Wards</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Westminster Hall</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Court of Upper Bench, sitting in Westminster Hall</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>sugar_loaf_tavern</t>
+          <t>exchequer_court</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sugar Loaf Tavern</t>
+          <t>Court of Exchequer</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Temple Bar</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>51.513455</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>-0.111742</v>
-      </c>
+          <t>Westminster Palace</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fleet Street, "a drinking-house near Temple Bar" 9 Feb, named "the Sugar Loaf by Temple Bar, where Swan and I were last night" 10 Feb 1659/60</t>
+          <t>"the Exchequer, where the Barons were hearing of causes" - the court, distinct from office_exchequer, Mr Downing's office</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>court_of_wards</t>
+          <t>commons_lobby</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Court of Wards</t>
+          <t>House of Commons Lobby</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Westminster</t>
+          <t>Westminster Palace</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
@@ -2775,124 +2783,124 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>exchequer_court</t>
+          <t>cookshop_unknown_2</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Court of Exchequer</t>
+          <t>Cookshop Unknown</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Westminster Palace</t>
+          <t>Temple Bar</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>"the Exchequer, where the Barons were hearing of causes" - the court, distinct from office_exchequer, Mr Downing's office</t>
+          <t>"within Temple Bar, we found a pullet ready roasted" 11 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>commons_lobby</t>
+          <t>rolls_office_chancery</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>House of Commons Lobby</t>
+          <t>The Rolls Office</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Westminster Palace</t>
+          <t>Chancery Lane</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Rolls Office and Chapel</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>cookshop_unknown_2</t>
+          <t>james_chetwind_office</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cookshop Unknown</t>
+          <t>James Chetwind Office</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Temple Bar</t>
+          <t>Chancery Lane</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>"within Temple Bar, we found a pullet ready roasted" 11 Feb 1659/60</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>rolls_office_chancery</t>
+          <t>guildhall</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The Rolls Office</t>
+          <t>Guildhall</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chancery Lane</t>
+          <t>City of London</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr"/>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Rolls Office and Chapel</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>james_chetwind_office</t>
+          <t>three_tuns_tavern</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>James Chetwind Office</t>
+          <t>Three Tuns Tavern</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chancery Lane</t>
+          <t>Guildhall Yard</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>"the 3 Tun tavern", near Guildhall</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>guildhall</t>
+          <t>alehouse_unknown_5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Guildhall</t>
+          <t>Alehouse Unknown</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2902,41 +2910,45 @@
       </c>
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Unnamed alehouse near Guildhall, 11 Feb 1659/60</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>three_tuns_tavern</t>
+          <t>merchant_house_unknown_1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Three Tuns Tavern</t>
+          <t>Merchant House Unknown</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Guildhall Yard</t>
+          <t>City of London</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>"the 3 Tun tavern", near Guildhall</t>
+          <t>"a merchant's house hard by" Guildhall, 11 Feb 1659/60; Sir Nicholas Crisp was there</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>alehouse_unknown_5</t>
+          <t>moorfields</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Alehouse Unknown</t>
+          <t>Moorfields</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2944,180 +2956,156 @@
           <t>City of London</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr"/>
-      <c r="E115" s="2" t="inlineStr"/>
+      <c r="D115" s="2" t="n">
+        <v>51.519038</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>-0.086882</v>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Unnamed alehouse near Guildhall, 11 Feb 1659/60</t>
+          <t>Near the Moorgate, divided into three areas Moorfields proper, Middle and Upper, near Bethlem Hospital Moorfields</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>merchant_house_unknown_1</t>
+          <t>john_playford_shop</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Merchant House Unknown</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>City of London</t>
-        </is>
-      </c>
+          <t>John Playford Shop</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>"a merchant's house hard by" Guildhall, 11 Feb 1659/60; Sir Nicholas Crisp was there</t>
+          <t>John Playford, music seller</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>moorfields</t>
+          <t>richard_cumberland_lodgings</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Moorfields</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>City of London</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>51.519038</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>-0.086882</v>
-      </c>
+          <t>Richard Cumberland Lodgings</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Near the Moorgate, divided into three areas Moorfields proper, Middle and Upper, near Bethlem Hospital Moorfields</t>
+          <t>Richard Cumberland, "newly come out of the country from his living" 5 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>john_playford_shop</t>
+          <t>michael_hering_house</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>John Playford Shop</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Michael Hering House</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>John Playford, music seller</t>
+          <t>Possibly located on Coleman Street, Hering the merchant, concerned in my Lord's Worcester money</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>richard_cumberland_lodgings</t>
+          <t>new_exchange</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Richard Cumberland Lodgings</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>The New Exchange</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>The Strand</t>
+        </is>
+      </c>
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Richard Cumberland, "newly come out of the country from his living" 5 Feb 1659/60</t>
+          <t>Shopping arcade on the south side of the Strand; distinct from the Royal Exchange in the City</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>michael_hering_house</t>
+          <t>new_palace_yard_westminster</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Michael Hering House</t>
+          <t>New Palace Yard</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>City of London</t>
+          <t>Westminster Palace</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Possibly located on Coleman Street, Hering the merchant, concerned in my Lord's Worcester money</t>
+          <t>"then to the Hall, where in the Palace I saw Monk's soldiers abuse Billing and all the Quakers" 7 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>new_exchange</t>
+          <t>exchequer_tavern_charing_cross</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>The New Exchange</t>
+          <t>The Exchequer Tavern</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>The Strand</t>
+          <t>Charing Cross</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Shopping arcade on the south side of the Strand; distinct from the Royal Exchange in the City</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>new_palace_yard_westminster</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>New Palace Yard</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Westminster Palace</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr"/>
-      <c r="E122" s="2" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>"then to the Hall, where in the Palace I saw Monk's soldiers abuse Billing and all the Quakers" 7 Feb 1659/60</t>
+          <t>"drank with him at the Exchequer at Charing Cross" 2 Feb 1659/60; kept distinct from chequers_inn</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F122"/>
+  <autoFilter ref="A1:F121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/node-list.xlsx
+++ b/node-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="nodes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3104,8 +3104,620 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>jacobs_alehouse</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Jacob's Alehouse</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>"drank a cup of ale at Jacob's" 17 Feb 1659/60, after walking in the park</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>wotton_shop</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Mr Wotton Shop</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" s="2" t="inlineStr"/>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Mr Wotton, shoemaker; first name not given in the diary</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_6</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Alehouse Unknown</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Fleet Street</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>"I to Mr. Wotton's, and with him to an alehouse" 18 Feb 1659/60, unnamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>marshes_whitehall</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Marsh's</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Whitehall Palace</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr"/>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>A drinking house at Whitehall; "to Marsh's at Whitehall to drink" 20 Feb, "at Marsh's" 22 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_7</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Alehouse Unknown</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>"thence I took them to drink, and so put off my uncle" 23 Feb 1659/60, unnamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>scotland_yard_stable</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Mr Garthwayt Stable</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Scotland Yard, Whitehall</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr"/>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>"taking horse at Scotland Yard, at Mr. Garthwayt's stable" 24 Feb 1659/60; the horse was lent to Pepys for the Cambridge journey</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>mrs_michells_shop</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Mrs Michell Shop</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Westminster Hall</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>A shop within Westminster Hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ware</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ware</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Hertfordshire</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>"About Ware we overtook Mr. Blayton" 24 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>puckeridge</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Puckeridge</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Hertfordshire</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>"at Puckeridge we baited, where we had a loin of mutton fried" 24 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>chequer_inn_foulmere</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>The Chequer Inn</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Foulmere, Cambridgeshire</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>"as far as Foulmer, within six miles of Cambridge ... here we lay at the Chequer" 24 Feb 1659/60. Distinct from chequers_inn and exchequer_tavern_charing_cross, both at Charing Cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>The Falcon Inn</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Petty Cury, Cambridge</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Pepys's lodging in Cambridge, 25-27 Feb 1659/60; "my Inn" throughout those entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>christs_college_cambridge</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Christ's College</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Cambridge</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr"/>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Mr Widdrington's chamber; Pepys's brother John was admitted here 25 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>magdalene_college_cambridge</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Magdalene College</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Cambridge</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Pepys's own college; Mr Hill's chambers</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>angier_house_cambridge</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Angier House</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Cambridge</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr"/>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Cousin Angier's house</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>mertons_shop_cambridge</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Mr Merton Shop</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Cambridge</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr"/>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Bookseller; Pepys bought 'Elenchus Motuum' here 25 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>three_tuns_tavern_cambridge</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Three Tuns Tavern</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Cambridge</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Distinct from three_tuns_tavern in Guildhall Yard, City of London</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>kings_college_cambridge</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>King's College</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Cambridge</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>"the fields behind King's College, and in King's College Chapel Yard" 26 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>st_botolphs_church_cambridge</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>St Botolph's Church</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Cambridge</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Mr Nicholas of Queen's College preached, 26 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>rose_tavern_cambridge</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Rose Tavern</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Cambridge</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>white_hart_saffron_walden</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>The White Hart Inn</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Saffron Walden, Essex</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>"at the White Hart, we set up our horses" 27 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>audley_end_house</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Audley End House</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Saffron Walden, Essex</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>"the stateliness of the ceilings, chimney-pieces, and form of the whole was exceedingly worth seeing" 27 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>almshouse_saffron_walden</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Almshouse</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Saffron Walden, Essex</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>"a very old hospital or almshouse, where forty poor people was maintained" 27 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>inn_epping</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Inn at Epping</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Epping, Essex</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Unnamed inn; Pepys lodged here the night of 27 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>st_pauls_cathedral</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>St Paul's Cathedral</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>St. Paul's Churchyard</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>"At Paul's I light ... I found Dr. Reynolds in the pulpit, and General Monk there" 28 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>plough_fleet_street</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>The Plough</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Fleet Street</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>A hatter's; Pepys bought a hat here by my Lord's direction, 28 Feb 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>greyhound_tavern</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Greyhound Tavern</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Fleet Street</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F121"/>
+  <autoFilter ref="A1:F147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/node-list.xlsx
+++ b/node-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="nodes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3131,12 +3131,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>wotton_shop</t>
+          <t>william_wotton_shop</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Mr Wotton Shop</t>
+          <t>William Wotton Shop</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -3144,7 +3144,7 @@
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mr Wotton, shoemaker; first name not given in the diary</t>
+          <t>William Wotton, shoemaker</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>mrs_michells_shop</t>
+          <t>anne_michell_shop</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mrs Michell Shop</t>
+          <t>Anne Michell Shop</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3264,14 +3264,14 @@
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>A shop within Westminster Hall</t>
+          <t>Mrs Anne Michell's shop, within Westminster Hall</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ware</t>
+          <t>ware_hertfordshire</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3295,7 +3295,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>puckeridge</t>
+          <t>puckeridge_hertfordshire</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3319,7 +3319,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>chequer_inn_foulmere</t>
+          <t>chequer_inn_fowlmere</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Foulmere, Cambridgeshire</t>
+          <t>Fowlmere, Cambridgeshire</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr"/>
@@ -3415,12 +3415,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>angier_house_cambridge</t>
+          <t>john_angier_house_cambridge</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Angier House</t>
+          <t>John Angier House</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3432,7 +3432,7 @@
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Cousin Angier's house</t>
+          <t>Cousin John Angier</t>
         </is>
       </c>
     </row>
@@ -3716,8 +3716,56 @@
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>sun_tavern_king_street</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>The Sun Tavern</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>King Street, Westminster</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>"we went to the Sun Tavern in expectation of a dinner" 16 Feb 1659/60; separate from the_sun_tavern in Chancery Lane</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>park_unknown_1</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Park Unknown</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr"/>
+      <c r="E149" s="2" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>"we went and walked in the park till it was dark. I played on my pipe at the Echo" 17 Feb 1659/60 - which park is not said</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F147"/>
+  <autoFilter ref="A1:F149"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/node-list.xlsx
+++ b/node-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="nodes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$182</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3764,8 +3764,768 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>laxton_apothecary</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Mr Laxton Apothecary</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>"Mr. Laxton's; my Lord's apothecary" 1 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>leg_tavern</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>The Leg</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>King Street, Westminster</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="2" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>"the Leg [another tavern] in King's street" 2 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>warwick_house</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Warwick House</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Holborn</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>"Warwick House, in Holborn"; Pepys waited in the great hall while my Lord dined, 3 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_8</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Alehouse Unknown</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr"/>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>"met Mr. Gifford, who took me and gave me half a pint of wine" 3 Mar 1659/60, unnamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_9</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Alehouse Unknown</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Drury Lane</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>"Tom Harper, who took me into a place in Drury Lane, where we drank a great deal of strong water" 3 Mar 1659/60, unnamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>salutation_tavern</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>The Salutation Tavern</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Billingsgate</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr"/>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>"by water to Billingsgate, at the Salutation Tavern" 5 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>pinkney_house</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Mr Pinkney House</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>"he shewed me how he had alway kept the Lion and Unicorn, in the back of his chimney, bright, in expectation of the King's coming again" 5 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>whitehall_garden</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Whitehall Garden</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Whitehall Palace</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr"/>
+      <c r="E157" s="2" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>"he called me by myself to go along with him into the garden" - where my Lord first asked Pepys to go to sea as his secretary, 6 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>bell_tavern</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>The Bell</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr"/>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>"I went to the Bell" for the carpenters' yearly Shrove Tuesday club, 6 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>lion_tavern</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>The Lion</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" s="2" t="inlineStr"/>
+      <c r="E159" s="2" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>"found him at the Lion with a pewterer" 6 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>st_jamess_palace</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>St James's Palace</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr"/>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>angel_tavern</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>The Angel</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>King Street, Westminster</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr"/>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>"the Angel in King Street, where Chetwind, Mr. Thomas and Doling were at oysters" 7 Mar 1659/60, the first day of Lent</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>popes_head_alley</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Pope's Head Alley</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr"/>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Adam Chard's, where Pepys bought a catcall, 7 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_10</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Alehouse Unknown</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr"/>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>"Thence went and gave him a cup of ale" 7 Mar 1659/60, unnamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>sun_tavern_behind_exchange</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>The Sun Tavern</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Behind the Royal Exchange, City of London</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>"the Sun behind the Exchange" 7 Mar 1659/60. A third Sun, distinct from the_sun_tavern (Chancery Lane) and sun_tavern_king_street</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>cock_tavern</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>The Cock</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>"a health or two round at the Cock" 7 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>dog_tavern</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>The Dog Tavern</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>"This noon I met at the Dog tavern Captain Philip Holland" 8 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>paternoster_row</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Paternoster Row</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr"/>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>"took my wife by land to Paternoster Row, to buy some Paragon for a petticoat" 8 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>The Admiralty</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Whitehall, Westminster</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr"/>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>painted_chamber</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>The Painted Chamber</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Westminster Palace</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr"/>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>St Edward's Chamber in the old Palace, named for its wall paintings</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>navy_office</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>The Navy Office</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Seething Lane, City of London</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr"/>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>"by coach, taking Mr. Butler with me to the Navy Office" 9 Mar 1659/60. Pepys moves into the adjoining house in July 1660</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>council_chamber_whitehall</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Council Chamber Whitehall</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Whitehall Palace</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr"/>
+      <c r="E171" s="2" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>navy_treasurer_office</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Navy Treasurer Office</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" s="2" t="inlineStr"/>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Mr Hutchinson, Treasurer for the Navy, cf. 8 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>rawlinson_house</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Mr Rawlinson House</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr"/>
+      <c r="E173" s="2" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>"having left L200 of it with Mr. Rawlinson at his house for Sheply" 10 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>sun_tavern_fish_street_hill</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>The Sun Tavern</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Fish Street Hill, City of London</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr"/>
+      <c r="E174" s="2" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>"the Sun tavern on Fish Street Hill" 10 Mar, and 15 Mar 1659/60. A fourth Sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>blackburne_house</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Mr Blackburne House</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" s="2" t="inlineStr"/>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Robert Blackburne, Secretary to the Admiralty</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>bedells_bookshop</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Bedell Bookshop</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Temple Gate</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr"/>
+      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>"Bedells the bookseller's at the Temple gate" 12 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>white_horse_king_street</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>The White Horse</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>King Street, Westminster</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr"/>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>"the White Horse in King Street, where I got Mr. Buddle's horse" 12 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>bowyer_house</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Mr Bowyer House</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Huntsmore, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr"/>
+      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Where Elizabeth Pepys was to board while Pepys was at sea; he lodged here the night of 12 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>roberts_whitehall</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Roberts</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Whitehall Palace</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr"/>
+      <c r="E179" s="2" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>"at drink with them at Roberts at Whitehall" 13 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>creeds_chamber</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Mr Creed Chamber</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" s="2" t="inlineStr"/>
+      <c r="E180" s="2" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>John Creed, deputy treasurer to the Fleet</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>fish_street</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Fish Street</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr"/>
+      <c r="E181" s="2" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>"in Fish Street my wife and I bought a bit of salmon" 15 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>fox_tavern</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>The Fox</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>King Street, Westminster</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr"/>
+      <c r="E182" s="2" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>"the Fox in King-street to supper on a brave turkey of Mr. Hawly's" 15 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F149"/>
+  <autoFilter ref="A1:F182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/node-list.xlsx
+++ b/node-list.xlsx
@@ -2303,148 +2303,148 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>house_of_commons</t>
+          <t>priors_rhenish_wine_house</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>House of Commons</t>
+          <t>Priors Rhenish Wine House</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Westminster Palace</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>"the manner of the Houses sitting" 3 Feb 1659/60</t>
+          <t>Cannon Row, Westminster, at the end of passage leading from King Street. "Priors, the Rhenish wine-house" 3 Feb; "a Rhenish wine house" 8 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>priors_rhenish_wine_house</t>
+          <t>palace_yard_westminster</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Priors Rhenish Wine House</t>
+          <t>Palace Yard Westminster</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Westminster</t>
+          <t>Westminster Palace</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cannon Row, Westminster, at the end of passage leading from King Street. "Priors, the Rhenish wine-house" 3 Feb; "a Rhenish wine house" 8 Feb 1659/60</t>
+          <t>The entry does not say whether New or Old Palace Yard</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>palace_yard_westminster</t>
+          <t>charing_cross</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Palace Yard Westminster</t>
+          <t>Charing Cross</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Westminster Palace</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>The entry does not say whether New or Old Palace Yard</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>charing_cross</t>
+          <t>william_swan_house</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Charing Cross</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Westminster</t>
-        </is>
-      </c>
+          <t>William Swan House</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>William Swan, of the Exchequer</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>william_swan_house</t>
+          <t>stephens_chamber_temple</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>William Swan House</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>Mr Stephens Chamber</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>The Temple</t>
+        </is>
+      </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>William Swan, of the Exchequer</t>
+          <t>"Mr. Downing's Counsellor" 1 Feb; "the Counsellor at the Temple, Mr. Stephens" 4 Feb; "Mr. Stevens our lawyer" 10 Feb 1659/60 - one person, acting in the Downing/Squib case throughout</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>stephens_chamber_temple</t>
+          <t>grays_inn</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mr Stephens Chamber</t>
+          <t>Gray's Inn</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>The Temple</t>
+          <t>Holborn</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>"Mr. Downing's Counsellor" 1 Feb; "the Counsellor at the Temple, Mr. Stephens" 4 Feb; "Mr. Stevens our lawyer" 10 Feb 1659/60 - one person, acting in the Downing/Squib case throughout</t>
+          <t>Inn of Court</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>grays_inn</t>
+          <t>alehouse_unknown_4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Gray's Inn</t>
+          <t>Alehouse Unknown</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2456,43 +2456,39 @@
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Inn of Court</t>
+          <t>"we met with an acquaintance of his in the walks, and went and drank" 4 Feb 1659/60 - drinking house near Gray's Inn, unnamed</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>alehouse_unknown_4</t>
+          <t>thomas_widdrington_house</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Alehouse Unknown</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Holborn</t>
-        </is>
-      </c>
+          <t>Lord Thomas Widdrington House</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>"we met with an acquaintance of his in the walks, and went and drank" 4 Feb 1659/60 - drinking house near Gray's Inn, unnamed</t>
+          <t>Mr Swan's master</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>thomas_widdrington_house</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lord Thomas Widdrington House</t>
+          <t>Scott House</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2500,251 +2496,255 @@
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mr Swan's master</t>
+          <t>Madam Scott and her husband. Mrs Jem (Jemima Montagu) lodges here through February 1659/60, with Mrs Ann; 4 Feb places both at Scott's explicitly</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>scott_house</t>
+          <t>bull_head_tavern</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Scott House</t>
+          <t>Bull Head Tavern</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Madam Scott and her husband. Mrs Jem (Jemima Montagu) lodges here through February 1659/60, with Mrs Ann; 4 Feb places both at Scott's explicitly</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>bull_head_tavern</t>
+          <t>the_temple</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bull Head Tavern</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>The Temple</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Temple district</t>
+        </is>
+      </c>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Area-level node for "the Temple" where no chamber is named</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>the_temple</t>
+          <t>st_pauls_school</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Temple</t>
+          <t>St Paul's School</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Temple district</t>
+          <t>St. Paul's Churchyard</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Area-level node for "the Temple" where no chamber is named</t>
+          <t>Pepys's own school; his brother John was a pupil</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>st_pauls_school</t>
+          <t>john_stone_office</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>St Paul's School</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>St. Paul's Churchyard</t>
-        </is>
-      </c>
+          <t>Captain John Stone Office</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pepys's own school; his brother John was a pupil</t>
+          <t>Captain Stone, concerned in Mr Downing's business</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>john_stone_office</t>
+          <t>temple_gardens</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Captain John Stone Office</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>Temple Gardens</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>The Temple</t>
+        </is>
+      </c>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Captain Stone, concerned in Mr Downing's business</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>temple_gardens</t>
+          <t>william_wheeler_house</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Temple Gardens</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>The Temple</t>
-        </is>
-      </c>
+          <t>Sir William Wheeler House</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Sir William Wheeler</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>william_wheeler_house</t>
+          <t>john_phelps_house</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sir William Wheeler House</t>
+          <t>John Phelps House</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Sir William Wheeler</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>john_phelps_house</t>
+          <t>upper_bench_court</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>John Phelps House</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>Upper Bench</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Westminster Hall</t>
+        </is>
+      </c>
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Court of Upper Bench, sitting in Westminster Hall</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>upper_bench_court</t>
+          <t>sugar_loaf_tavern</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Upper Bench</t>
+          <t>Sugar Loaf Tavern</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Westminster Hall</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr"/>
-      <c r="E103" s="2" t="inlineStr"/>
+          <t>Temple Bar</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>51.513455</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>-0.111742</v>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Court of Upper Bench, sitting in Westminster Hall</t>
+          <t>Fleet Street, "a drinking-house near Temple Bar" 9 Feb, named "the Sugar Loaf by Temple Bar, where Swan and I were last night" 10 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>sugar_loaf_tavern</t>
+          <t>court_of_wards</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sugar Loaf Tavern</t>
+          <t>Court of Wards</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Temple Bar</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>51.513455</v>
-      </c>
-      <c r="E104" s="2" t="n">
-        <v>-0.111742</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Fleet Street, "a drinking-house near Temple Bar" 9 Feb, named "the Sugar Loaf by Temple Bar, where Swan and I were last night" 10 Feb 1659/60</t>
-        </is>
-      </c>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>court_of_wards</t>
+          <t>exchequer_court</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Court of Wards</t>
+          <t>Court of Exchequer</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Westminster</t>
+          <t>Westminster Palace</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>"the Exchequer, where the Barons were hearing of causes" - the court, distinct from office_exchequer, Mr Downing's office</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>exchequer_court</t>
+          <t>commons_lobby</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Court of Exchequer</t>
+          <t>House of Commons Lobby</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2754,65 +2754,65 @@
       </c>
       <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>"the Exchequer, where the Barons were hearing of causes" - the court, distinct from office_exchequer, Mr Downing's office</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>commons_lobby</t>
+          <t>cookshop_unknown_2</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>House of Commons Lobby</t>
+          <t>Cookshop Unknown</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Westminster Palace</t>
+          <t>Temple Bar</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>"within Temple Bar, we found a pullet ready roasted" 11 Feb 1659/60</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>cookshop_unknown_2</t>
+          <t>rolls_office_chancery</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cookshop Unknown</t>
+          <t>The Rolls Office</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Temple Bar</t>
+          <t>Chancery Lane</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>"within Temple Bar, we found a pullet ready roasted" 11 Feb 1659/60</t>
+          <t>Rolls Office and Chapel</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>rolls_office_chancery</t>
+          <t>james_chetwind_office</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The Rolls Office</t>
+          <t>James Chetwind Office</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2822,26 +2822,22 @@
       </c>
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Rolls Office and Chapel</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>james_chetwind_office</t>
+          <t>guildhall</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>James Chetwind Office</t>
+          <t>Guildhall</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chancery Lane</t>
+          <t>City of London</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
@@ -2851,56 +2847,60 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>guildhall</t>
+          <t>three_tuns_tavern</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Guildhall</t>
+          <t>Three Tuns Tavern</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>City of London</t>
+          <t>Guildhall Yard</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>"the 3 Tun tavern", near Guildhall</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>three_tuns_tavern</t>
+          <t>alehouse_unknown_5</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Three Tuns Tavern</t>
+          <t>Alehouse Unknown</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Guildhall Yard</t>
+          <t>City of London</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>"the 3 Tun tavern", near Guildhall</t>
+          <t>Unnamed alehouse near Guildhall, 11 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>alehouse_unknown_5</t>
+          <t>merchant_house_unknown_1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Alehouse Unknown</t>
+          <t>Merchant House Unknown</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2912,19 +2912,19 @@
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Unnamed alehouse near Guildhall, 11 Feb 1659/60</t>
+          <t>"a merchant's house hard by" Guildhall, 11 Feb 1659/60; Sir Nicholas Crisp was there</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>merchant_house_unknown_1</t>
+          <t>moorfields</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Merchant House Unknown</t>
+          <t>Moorfields</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2932,51 +2932,47 @@
           <t>City of London</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr"/>
-      <c r="E114" s="2" t="inlineStr"/>
+      <c r="D114" s="2" t="n">
+        <v>51.519038</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>-0.086882</v>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>"a merchant's house hard by" Guildhall, 11 Feb 1659/60; Sir Nicholas Crisp was there</t>
+          <t>Near the Moorgate, divided into three areas Moorfields proper, Middle and Upper, near Bethlem Hospital Moorfields</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>moorfields</t>
+          <t>john_playford_shop</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Moorfields</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>City of London</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>51.519038</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>-0.086882</v>
-      </c>
+          <t>John Playford Shop</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Near the Moorgate, divided into three areas Moorfields proper, Middle and Upper, near Bethlem Hospital Moorfields</t>
+          <t>John Playford, music seller</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>john_playford_shop</t>
+          <t>richard_cumberland_lodgings</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>John Playford Shop</t>
+          <t>Richard Cumberland Lodgings</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2984,299 +2980,303 @@
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>John Playford, music seller</t>
+          <t>Richard Cumberland, "newly come out of the country from his living" 5 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>richard_cumberland_lodgings</t>
+          <t>michael_hering_house</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Richard Cumberland Lodgings</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Michael Hering House</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
       <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Richard Cumberland, "newly come out of the country from his living" 5 Feb 1659/60</t>
+          <t>Possibly located on Coleman Street, Hering the merchant, concerned in my Lord's Worcester money</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>michael_hering_house</t>
+          <t>new_exchange</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Michael Hering House</t>
+          <t>The New Exchange</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>City of London</t>
+          <t>The Strand</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Possibly located on Coleman Street, Hering the merchant, concerned in my Lord's Worcester money</t>
+          <t>Shopping arcade on the south side of the Strand; distinct from the Royal Exchange in the City</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>new_exchange</t>
+          <t>new_palace_yard_westminster</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>The New Exchange</t>
+          <t>New Palace Yard</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>The Strand</t>
+          <t>Westminster Palace</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Shopping arcade on the south side of the Strand; distinct from the Royal Exchange in the City</t>
+          <t>"then to the Hall, where in the Palace I saw Monk's soldiers abuse Billing and all the Quakers" 7 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>new_palace_yard_westminster</t>
+          <t>exchequer_tavern_charing_cross</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>New Palace Yard</t>
+          <t>The Exchequer Tavern</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Westminster Palace</t>
+          <t>Charing Cross</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>"then to the Hall, where in the Palace I saw Monk's soldiers abuse Billing and all the Quakers" 7 Feb 1659/60</t>
+          <t>"drank with him at the Exchequer at Charing Cross" 2 Feb 1659/60; kept distinct from chequers_inn</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>exchequer_tavern_charing_cross</t>
+          <t>jacobs_alehouse</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>The Exchequer Tavern</t>
+          <t>Jacob's Alehouse</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Charing Cross</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>"drank with him at the Exchequer at Charing Cross" 2 Feb 1659/60; kept distinct from chequers_inn</t>
+          <t>"drank a cup of ale at Jacob's" 17 Feb 1659/60, after walking in the park</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>jacobs_alehouse</t>
+          <t>william_wotton_shop</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jacob's Alehouse</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Westminster</t>
-        </is>
-      </c>
+          <t>William Wotton Shop</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>"drank a cup of ale at Jacob's" 17 Feb 1659/60, after walking in the park</t>
+          <t>William Wotton, shoemaker</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>william_wotton_shop</t>
+          <t>alehouse_unknown_6</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>William Wotton Shop</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>Alehouse Unknown</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Fleet Street</t>
+        </is>
+      </c>
       <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>William Wotton, shoemaker</t>
+          <t>"I to Mr. Wotton's, and with him to an alehouse" 18 Feb 1659/60, unnamed</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>alehouse_unknown_6</t>
+          <t>marshes_whitehall</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Alehouse Unknown</t>
+          <t>Marsh's</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Fleet Street</t>
+          <t>Whitehall Palace</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>"I to Mr. Wotton's, and with him to an alehouse" 18 Feb 1659/60, unnamed</t>
+          <t>A drinking house at Whitehall; "to Marsh's at Whitehall to drink" 20 Feb, "at Marsh's" 22 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>marshes_whitehall</t>
+          <t>alehouse_unknown_7</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Marsh's</t>
+          <t>Alehouse Unknown</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Whitehall Palace</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>A drinking house at Whitehall; "to Marsh's at Whitehall to drink" 20 Feb, "at Marsh's" 22 Feb 1659/60</t>
+          <t>"thence I took them to drink, and so put off my uncle" 23 Feb 1659/60, unnamed</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>alehouse_unknown_7</t>
+          <t>scotland_yard_stable</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Alehouse Unknown</t>
+          <t>Mr Garthwayt Stable</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Westminster</t>
+          <t>Scotland Yard, Whitehall</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>"thence I took them to drink, and so put off my uncle" 23 Feb 1659/60, unnamed</t>
+          <t>"taking horse at Scotland Yard, at Mr. Garthwayt's stable" 24 Feb 1659/60; the horse was lent to Pepys for the Cambridge journey</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>scotland_yard_stable</t>
+          <t>anne_michell_shop</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mr Garthwayt Stable</t>
+          <t>Anne Michell Shop</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Yard, Whitehall</t>
+          <t>Westminster Hall</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>"taking horse at Scotland Yard, at Mr. Garthwayt's stable" 24 Feb 1659/60; the horse was lent to Pepys for the Cambridge journey</t>
+          <t>Mrs Anne Michell's shop, within Westminster Hall</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>anne_michell_shop</t>
+          <t>ware_hertfordshire</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Anne Michell Shop</t>
+          <t>Ware</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Westminster Hall</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mrs Anne Michell's shop, within Westminster Hall</t>
+          <t>"About Ware we overtook Mr. Blayton" 24 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ware_hertfordshire</t>
+          <t>puckeridge_hertfordshire</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ware</t>
+          <t>Puckeridge</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3288,91 +3288,91 @@
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>"About Ware we overtook Mr. Blayton" 24 Feb 1659/60</t>
+          <t>"at Puckeridge we baited, where we had a loin of mutton fried" 24 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>puckeridge_hertfordshire</t>
+          <t>chequer_inn_fowlmere</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Puckeridge</t>
+          <t>The Chequer Inn</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Fowlmere, Cambridgeshire</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>"at Puckeridge we baited, where we had a loin of mutton fried" 24 Feb 1659/60</t>
+          <t>"as far as Foulmer, within six miles of Cambridge ... here we lay at the Chequer" 24 Feb 1659/60. Distinct from chequers_inn and exchequer_tavern_charing_cross, both at Charing Cross</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>chequer_inn_fowlmere</t>
+          <t>falcon_inn_cambridge</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>The Chequer Inn</t>
+          <t>The Falcon Inn</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Fowlmere, Cambridgeshire</t>
+          <t>Petty Cury, Cambridge</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr"/>
       <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>"as far as Foulmer, within six miles of Cambridge ... here we lay at the Chequer" 24 Feb 1659/60. Distinct from chequers_inn and exchequer_tavern_charing_cross, both at Charing Cross</t>
+          <t>Pepys's lodging in Cambridge, 25-27 Feb 1659/60; "my Inn" throughout those entries</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>falcon_inn_cambridge</t>
+          <t>christs_college_cambridge</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>The Falcon Inn</t>
+          <t>Christ's College</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Petty Cury, Cambridge</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr"/>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pepys's lodging in Cambridge, 25-27 Feb 1659/60; "my Inn" throughout those entries</t>
+          <t>Mr Widdrington's chamber; Pepys's brother John was admitted here 25 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>christs_college_cambridge</t>
+          <t>magdalene_college_cambridge</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Christ's College</t>
+          <t>Magdalene College</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3384,19 +3384,19 @@
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mr Widdrington's chamber; Pepys's brother John was admitted here 25 Feb 1659/60</t>
+          <t>Pepys's own college; Mr Hill's chambers</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>magdalene_college_cambridge</t>
+          <t>john_angier_house_cambridge</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Magdalene College</t>
+          <t>John Angier House</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3408,19 +3408,19 @@
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pepys's own college; Mr Hill's chambers</t>
+          <t>Cousin John Angier</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>john_angier_house_cambridge</t>
+          <t>mertons_shop_cambridge</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>John Angier House</t>
+          <t>Mr Merton Shop</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3432,19 +3432,19 @@
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Cousin John Angier</t>
+          <t>Bookseller; Pepys bought 'Elenchus Motuum' here 25 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>mertons_shop_cambridge</t>
+          <t>three_tuns_tavern_cambridge</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Mr Merton Shop</t>
+          <t>Three Tuns Tavern</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3456,19 +3456,19 @@
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bookseller; Pepys bought 'Elenchus Motuum' here 25 Feb 1659/60</t>
+          <t>Distinct from three_tuns_tavern in Guildhall Yard, City of London</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>three_tuns_tavern_cambridge</t>
+          <t>kings_college_cambridge</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Three Tuns Tavern</t>
+          <t>King's College</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3480,19 +3480,19 @@
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Distinct from three_tuns_tavern in Guildhall Yard, City of London</t>
+          <t>"the fields behind King's College, and in King's College Chapel Yard" 26 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kings_college_cambridge</t>
+          <t>st_botolphs_church_cambridge</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>King's College</t>
+          <t>St Botolph's Church</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3504,19 +3504,19 @@
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>"the fields behind King's College, and in King's College Chapel Yard" 26 Feb 1659/60</t>
+          <t>Mr Nicholas of Queen's College preached, 26 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>st_botolphs_church_cambridge</t>
+          <t>rose_tavern_cambridge</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>St Botolph's Church</t>
+          <t>Rose Tavern</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3526,41 +3526,41 @@
       </c>
       <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Mr Nicholas of Queen's College preached, 26 Feb 1659/60</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rose_tavern_cambridge</t>
+          <t>white_hart_saffron_walden</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Rose Tavern</t>
+          <t>The White Hart Inn</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Saffron Walden, Essex</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="2" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>"at the White Hart, we set up our horses" 27 Feb 1659/60</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>white_hart_saffron_walden</t>
+          <t>audley_end_house</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>The White Hart Inn</t>
+          <t>Audley End House</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3572,19 +3572,19 @@
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>"at the White Hart, we set up our horses" 27 Feb 1659/60</t>
+          <t>"the stateliness of the ceilings, chimney-pieces, and form of the whole was exceedingly worth seeing" 27 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>audley_end_house</t>
+          <t>almshouse_saffron_walden</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Audley End House</t>
+          <t>Almshouse</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3596,91 +3596,91 @@
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>"the stateliness of the ceilings, chimney-pieces, and form of the whole was exceedingly worth seeing" 27 Feb 1659/60</t>
+          <t>"a very old hospital or almshouse, where forty poor people was maintained" 27 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>almshouse_saffron_walden</t>
+          <t>inn_epping</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Almshouse</t>
+          <t>Inn at Epping</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Saffron Walden, Essex</t>
+          <t>Epping, Essex</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="2" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>"a very old hospital or almshouse, where forty poor people was maintained" 27 Feb 1659/60</t>
+          <t>Unnamed inn; Pepys lodged here the night of 27 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>inn_epping</t>
+          <t>st_pauls_cathedral</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Inn at Epping</t>
+          <t>St Paul's Cathedral</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Epping, Essex</t>
+          <t>St. Paul's Churchyard</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Unnamed inn; Pepys lodged here the night of 27 Feb 1659/60</t>
+          <t>"At Paul's I light ... I found Dr. Reynolds in the pulpit, and General Monk there" 28 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>st_pauls_cathedral</t>
+          <t>plough_fleet_street</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>St Paul's Cathedral</t>
+          <t>The Plough</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>St. Paul's Churchyard</t>
+          <t>Fleet Street</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>"At Paul's I light ... I found Dr. Reynolds in the pulpit, and General Monk there" 28 Feb 1659/60</t>
+          <t>A hatter's; Pepys bought a hat here by my Lord's direction, 28 Feb 1659/60</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>plough_fleet_street</t>
+          <t>greyhound_tavern</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>The Plough</t>
+          <t>Greyhound Tavern</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3690,156 +3690,156 @@
       </c>
       <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="2" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>A hatter's; Pepys bought a hat here by my Lord's direction, 28 Feb 1659/60</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>greyhound_tavern</t>
+          <t>sun_tavern_king_street</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Greyhound Tavern</t>
+          <t>The Sun Tavern</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Fleet Street</t>
+          <t>King Street, Westminster</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="2" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>"we went to the Sun Tavern in expectation of a dinner" 16 Feb 1659/60; separate from the_sun_tavern in Chancery Lane</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sun_tavern_king_street</t>
+          <t>park_unknown_1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>The Sun Tavern</t>
+          <t>Park Unknown</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>King Street, Westminster</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr"/>
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>"we went to the Sun Tavern in expectation of a dinner" 16 Feb 1659/60; separate from the_sun_tavern in Chancery Lane</t>
+          <t>"we went and walked in the park till it was dark. I played on my pipe at the Echo" 17 Feb 1659/60 - which park is not said</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>park_unknown_1</t>
+          <t>john_layton_apothecary</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Park Unknown</t>
+          <t>John Layton Apothecary</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>City of London</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>"we went and walked in the park till it was dark. I played on my pipe at the Echo" 17 Feb 1659/60 - which park is not said</t>
+          <t>My Lord's apothecary; "Mr. Laxton's" as the diary spells it, 1 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>laxton_apothecary</t>
+          <t>leg_tavern_king_st</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Mr Laxton Apothecary</t>
+          <t>The Leg</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>City of London</t>
+          <t>King Street, Westminster</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr"/>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>"Mr. Laxton's; my Lord's apothecary" 1 Mar 1659/60</t>
+          <t>"the Leg [another tavern] in King's street" 2 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>leg_tavern</t>
+          <t>warwick_house</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>The Leg</t>
+          <t>Warwick House</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>King Street, Westminster</t>
+          <t>Holborn</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr"/>
       <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>"the Leg [another tavern] in King's street" 2 Mar 1659/60</t>
+          <t>"Warwick House, in Holborn"; Pepys waited in the great hall while my Lord dined, 3 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>warwick_house</t>
+          <t>alehouse_unknown_8</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Warwick House</t>
+          <t>Alehouse Unknown</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Holborn</t>
+          <t>City of London</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr"/>
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>"Warwick House, in Holborn"; Pepys waited in the great hall while my Lord dined, 3 Mar 1659/60</t>
+          <t>"met Mr. Gifford, who took me and gave me half a pint of wine" 3 Mar 1659/60, unnamed</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>alehouse_unknown_8</t>
+          <t>alehouse_unknown_9</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3849,210 +3849,214 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>City of London</t>
+          <t>Drury Lane</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr"/>
       <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>"met Mr. Gifford, who took me and gave me half a pint of wine" 3 Mar 1659/60, unnamed</t>
+          <t>"Tom Harper, who took me into a place in Drury Lane, where we drank a great deal of strong water" 3 Mar 1659/60, unnamed</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>alehouse_unknown_9</t>
+          <t>salutation_tavern</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Alehouse Unknown</t>
+          <t>The Salutation Tavern</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Drury Lane</t>
+          <t>Billingsgate</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr"/>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>"Tom Harper, who took me into a place in Drury Lane, where we drank a great deal of strong water" 3 Mar 1659/60, unnamed</t>
+          <t>"by water to Billingsgate, at the Salutation Tavern" 5 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>salutation_tavern</t>
+          <t>george_pinkney_house</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>The Salutation Tavern</t>
+          <t>George Pinkney House</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Billingsgate</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr"/>
       <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>"by water to Billingsgate, at the Salutation Tavern" 5 Mar 1659/60</t>
+          <t>"he shewed me how he had alway kept the Lion and Unicorn, in the back of his chimney, bright, in expectation of the King's coming again" 5 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>pinkney_house</t>
+          <t>whitehall_garden</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mr Pinkney House</t>
+          <t>Whitehall Garden</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Westminster</t>
+          <t>Whitehall Palace</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr"/>
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>"he shewed me how he had alway kept the Lion and Unicorn, in the back of his chimney, bright, in expectation of the King's coming again" 5 Mar 1659/60</t>
+          <t>"he called me by myself to go along with him into the garden" - where my Lord first asked Pepys to go to sea as his secretary, 6 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>whitehall_garden</t>
+          <t>bell_tavern</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Whitehall Garden</t>
+          <t>The Bell</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Whitehall Palace</t>
+          <t>King Street, Westminster</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr"/>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>"he called me by myself to go along with him into the garden" - where my Lord first asked Pepys to go to sea as his secretary, 6 Mar 1659/60</t>
+          <t>"I went to the Bell" for the carpenters' yearly Shrove Tuesday club, 6 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>bell_tavern</t>
+          <t>red_lion_tavern</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>The Bell</t>
+          <t>The Red Lion</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Westminster</t>
+          <t>King Street, Westminster</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr"/>
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>"I went to the Bell" for the carpenters' yearly Shrove Tuesday club, 6 Mar 1659/60</t>
+          <t>"found him at the Lion with a pewterer" 6 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>lion_tavern</t>
+          <t>st_jamess_palace</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>The Lion</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
+          <t>St James's Palace</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
       <c r="D159" s="2" t="inlineStr"/>
       <c r="E159" s="2" t="inlineStr"/>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>"found him at the Lion with a pewterer" 6 Mar 1659/60</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>st_jamess_palace</t>
+          <t>angel_tavern</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>St James's Palace</t>
+          <t>The Angel</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Westminster</t>
+          <t>King Street, Westminster</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr"/>
       <c r="E160" s="2" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>"the Angel in King Street, where Chetwind, Mr. Thomas and Doling were at oysters" 7 Mar 1659/60, the first day of Lent</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>angel_tavern</t>
+          <t>popes_head_alley</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>The Angel</t>
+          <t>Pope's Head Alley</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>King Street, Westminster</t>
+          <t>City of London</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr"/>
       <c r="E161" s="2" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>"the Angel in King Street, where Chetwind, Mr. Thomas and Doling were at oysters" 7 Mar 1659/60, the first day of Lent</t>
+          <t>Adam Chard's, where Pepys bought a catcall, 7 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>popes_head_alley</t>
+          <t>alehouse_unknown_10</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Pope's Head Alley</t>
+          <t>Alehouse Unknown</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4064,463 +4068,463 @@
       <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Adam Chard's, where Pepys bought a catcall, 7 Mar 1659/60</t>
+          <t>"Thence went and gave him a cup of ale" 7 Mar 1659/60, unnamed</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>alehouse_unknown_10</t>
+          <t>sun_tavern_threadneedle_st</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Alehouse Unknown</t>
+          <t>The Sun Tavern</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>City of London</t>
+          <t>Behind the Royal Exchange, City of London</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
       <c r="E163" s="2" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>"Thence went and gave him a cup of ale" 7 Mar 1659/60, unnamed</t>
+          <t>"the Sun behind the Exchange" 7 Mar 1659/60. A third Sun, distinct from the_sun_tavern (Chancery Lane) and sun_tavern_king_street</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sun_tavern_behind_exchange</t>
+          <t>cock_tavern</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>The Sun Tavern</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Behind the Royal Exchange, City of London</t>
-        </is>
-      </c>
+          <t>The Cock Tavern</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" s="2" t="inlineStr"/>
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>"the Sun behind the Exchange" 7 Mar 1659/60. A third Sun, distinct from the_sun_tavern (Chancery Lane) and sun_tavern_king_street</t>
+          <t>"a health or two round at the Cock" 7 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>cock_tavern</t>
+          <t>dog_tavern</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>The Cock</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
+          <t>The Dog Tavern</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
       <c r="D165" s="2" t="inlineStr"/>
       <c r="E165" s="2" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>"a health or two round at the Cock" 7 Mar 1659/60</t>
+          <t>Next to the Mitre on King St and New Palace Yard. "This noon I met at the Dog tavern Captain Philip Holland" 8 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>dog_tavern</t>
+          <t>paternoster_row</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>The Dog Tavern</t>
+          <t>Paternoster Row</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Westminster</t>
+          <t>City of London</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr"/>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>"This noon I met at the Dog tavern Captain Philip Holland" 8 Mar 1659/60</t>
+          <t>"took my wife by land to Paternoster Row, to buy some Paragon for a petticoat" 8 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>paternoster_row</t>
+          <t>admiralty</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Paternoster Row</t>
+          <t>The Admiralty</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>City of London</t>
+          <t>Whitehall, Westminster</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr"/>
       <c r="E167" s="2" t="inlineStr"/>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>"took my wife by land to Paternoster Row, to buy some Paragon for a petticoat" 8 Mar 1659/60</t>
-        </is>
-      </c>
+      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>admiralty</t>
+          <t>painted_chamber_westminster</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>The Admiralty</t>
+          <t>The Painted Chamber</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Whitehall, Westminster</t>
+          <t>Westminster Palace</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr"/>
       <c r="E168" s="2" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>St Edward's Chamber in the old Palace, named for its wall paintings</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>painted_chamber</t>
+          <t>navy_office</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>The Painted Chamber</t>
+          <t>The Navy Office</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Westminster Palace</t>
+          <t>Seething Lane, City of London</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr"/>
       <c r="E169" s="2" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>St Edward's Chamber in the old Palace, named for its wall paintings</t>
+          <t>"by coach, taking Mr. Butler with me to the Navy Office" 9 Mar 1659/60. Pepys moves into the adjoining house in July 1660</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>navy_office</t>
+          <t>council_chamber_whitehall</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>The Navy Office</t>
+          <t>Council Chamber Whitehall</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Seething Lane, City of London</t>
+          <t>Whitehall Palace</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr"/>
       <c r="E170" s="2" t="inlineStr"/>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>"by coach, taking Mr. Butler with me to the Navy Office" 9 Mar 1659/60. Pepys moves into the adjoining house in July 1660</t>
-        </is>
-      </c>
+      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>council_chamber_whitehall</t>
+          <t>navy_treasurer_office</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Council Chamber Whitehall</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Whitehall Palace</t>
-        </is>
-      </c>
+          <t>Navy Treasurer Office</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" s="2" t="inlineStr"/>
       <c r="E171" s="2" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Mr Hutchinson, Treasurer for the Navy, cf. 8 Mar 1659/60</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>navy_treasurer_office</t>
+          <t>daniel_rawlinson_house</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Navy Treasurer Office</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>Daniel Rawlinson House</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
       <c r="D172" s="2" t="inlineStr"/>
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mr Hutchinson, Treasurer for the Navy, cf. 8 Mar 1659/60</t>
+          <t>"having left L200 of it with Mr. Rawlinson at his house for Sheply" 10 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>rawlinson_house</t>
+          <t>sun_tavern_fish_street_hill</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Mr Rawlinson House</t>
+          <t>The Sun Tavern</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>City of London</t>
+          <t>Fish Street Hill, City of London</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr"/>
       <c r="E173" s="2" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>"having left L200 of it with Mr. Rawlinson at his house for Sheply" 10 Mar 1659/60</t>
+          <t>"the Sun tavern on Fish Street Hill" 10 Mar, and 15 Mar 1659/60. A fourth Sun</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>sun_tavern_fish_street_hill</t>
+          <t>robert_blackborne_house</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>The Sun Tavern</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Fish Street Hill, City of London</t>
-        </is>
-      </c>
+          <t>Robert Blackborne House</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" s="2" t="inlineStr"/>
       <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>"the Sun tavern on Fish Street Hill" 10 Mar, and 15 Mar 1659/60. A fourth Sun</t>
+          <t>Robert Blackborne, Secretary to the Admiralty</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>blackburne_house</t>
+          <t>bedells_bookshop</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mr Blackburne House</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr"/>
+          <t>Bedell Bookshop</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Temple Gate, Fleet St</t>
+        </is>
+      </c>
       <c r="D175" s="2" t="inlineStr"/>
       <c r="E175" s="2" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Robert Blackburne, Secretary to the Admiralty</t>
+          <t>"Bedells the bookseller's at the Temple gate" 12 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>bedells_bookshop</t>
+          <t>white_horse_king_street</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Bedell Bookshop</t>
+          <t>The White Horse</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Temple Gate</t>
+          <t>King Street, Westminster</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr"/>
       <c r="E176" s="2" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>"Bedells the bookseller's at the Temple gate" 12 Mar 1659/60</t>
+          <t>"the White Horse in King Street, where I got Mr. Buddle's horse" 12 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>white_horse_king_street</t>
+          <t>robert_bowyer_house</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>The White Horse</t>
+          <t>Mr Bowyer House</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>King Street, Westminster</t>
+          <t>Huntsmoor, Buckinghamshire</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr"/>
       <c r="E177" s="2" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>"the White Horse in King Street, where I got Mr. Buddle's horse" 12 Mar 1659/60</t>
+          <t>Where Elizabeth Pepys was to board while Pepys was at sea; he lodged here the night of 12 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>bowyer_house</t>
+          <t>roberts_whitehall</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Mr Bowyer House</t>
+          <t>Roberts</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Huntsmore, Buckinghamshire</t>
+          <t>Whitehall Palace</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr"/>
       <c r="E178" s="2" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Where Elizabeth Pepys was to board while Pepys was at sea; he lodged here the night of 12 Mar 1659/60</t>
+          <t>"at drink with them at Roberts at Whitehall" 13 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>roberts_whitehall</t>
+          <t>john_creed_chamber</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Roberts</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Whitehall Palace</t>
-        </is>
-      </c>
+          <t>John Creed Chamber</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" s="2" t="inlineStr"/>
       <c r="E179" s="2" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>"at drink with them at Roberts at Whitehall" 13 Mar 1659/60</t>
+          <t>John Creed, deputy treasurer to the Fleet</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>creeds_chamber</t>
+          <t>fish_street_london</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Mr Creed Chamber</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr"/>
+          <t>Fish Street</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
       <c r="D180" s="2" t="inlineStr"/>
       <c r="E180" s="2" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>John Creed, deputy treasurer to the Fleet</t>
+          <t>"in Fish Street my wife and I bought a bit of salmon" 15 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>fish_street</t>
+          <t>fox_tavern</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Fish Street</t>
+          <t>The Fox</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>City of London</t>
+          <t>King Street, Westminster</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr"/>
       <c r="E181" s="2" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>"in Fish Street my wife and I bought a bit of salmon" 15 Mar 1659/60</t>
+          <t>"the Fox in King-street to supper on a brave turkey of Mr. Hawly's" 15 Mar 1659/60</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>fox_tavern</t>
+          <t>shotts_woodmonger_whitehall</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>The Fox</t>
+          <t>Shott's</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>King Street, Westminster</t>
+          <t>Whitehall, Westminster</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr"/>
       <c r="E182" s="2" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>"the Fox in King-street to supper on a brave turkey of Mr. Hawly's" 15 Mar 1659/60</t>
+          <t>A woodmonger. "To Whitehall to bespeak some firing for my father at Shott's" 8 Mar 1659/60</t>
         </is>
       </c>
     </row>

--- a/node-list.xlsx
+++ b/node-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="nodes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'nodes'!$A$1:$F$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4528,8 +4528,252 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>chequer_inn_holborn</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>The Chequer</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Holborn</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr"/>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>"took my wife by coach to the Chequer in Holborn" 17 Mar 1659/60, where Elizabeth Pepys took the coach for Huntsmoor. A fourth Chequer, distinct from chequers_inn and exchequer_tavern_charing_cross (Charing Cross) and chequer_inn_fowlmere</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>crisp_house</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Mrs Crisp House</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Axe Yard, Westminster</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr"/>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>"his mother's house by me in Axe Yard". Pepys lodged here the nights of 17-21 March 1659/60, his wife gone to Huntsmoor and his own house locked up</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>jervas_barber</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Jervas the Barber</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Palace Yard, Westminster</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr"/>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>"the barber's (Jervas) in Palace Yard" 18 Mar; Pepys began hiring his man to go to sea</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_11</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Alehouse Unknown</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Drury Lane</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr"/>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>"Mr. Woodfine, who took me to an alehouse in Drury Lane" 18 Mar 1659/60, unnamed; a separate occasion from alehouse_unknown_9</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>blagrave_house</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Mr Blagrave House</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" s="2" t="inlineStr"/>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>"called at Mr. Blagrave's, where I took up my note that he had of mine for 40s." 18 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>tavern_unknown_1</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Tavern Unknown</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" s="2" t="inlineStr"/>
+      <c r="E188" s="2" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>"a tavern over against Mr. Pierce's" 21 Mar 1659/60, unnamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>popes_head_tavern_chancery_lane</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>The Pope's Head Tavern</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Chancery Lane</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr"/>
+      <c r="E189" s="2" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>"the Pope's Head Tavern in Chancery Lane" 22 Mar 1659/60; distinct from popes_head_alley in the City</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>mounts_chamber</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Mr Mount Chamber</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" s="2" t="inlineStr"/>
+      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>"Doling and Luellin would have me go with them to Mount's chamber" 22 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>william_montagu_chamber</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>William Montagu Chamber</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" s="2" t="inlineStr"/>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>"carried my Lord's will in a black box to Mr. William Montagu for him to keep" 23 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>tower_of_london</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Tower of London</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr"/>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>"to the Tower, where the barges staid for us" 23 Mar 1659/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>swiftsure</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>The Swiftsure</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" s="2" t="inlineStr"/>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>My Lord's ship until the Naseby was ready. Pepys boarded 23 Mar 1659/60 and lived aboard; she lay in Long Reach, fell into the Hope on 27 March and lay below Gravesend from the 29th. A named ship is one node however far she sails (README 13-14)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F182"/>
+  <autoFilter ref="A1:F193"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>